--- a/fixed.xlsx
+++ b/fixed.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$I$587</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$I$596</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2642" uniqueCount="1134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2724" uniqueCount="1172">
   <si>
     <t>Nouvelles Références 2025</t>
   </si>
@@ -3430,6 +3430,120 @@
   </si>
   <si>
     <t>Benne à ridelles BRS 8004 40 km/h Pneu. sans porte arrière</t>
+  </si>
+  <si>
+    <t>BETAILLERE SALON HSRB 6134 FA DLP BARR-BACHE-CLOISON-BEQUI HYD + POMPE -PORTE OUTILS</t>
+  </si>
+  <si>
+    <t>PLATEAU SALON 12 TDI 20</t>
+  </si>
+  <si>
+    <t>PLATEAU SALON T 10012</t>
+  </si>
+  <si>
+    <t>PLATEAU SALON SP 8010 + BEQUILLE HYDRAU (pas encore homolo)</t>
+  </si>
+  <si>
+    <t>BRR 9004 SALON + REHAUSSE 0,50 + PORTE 2 BATTANTS</t>
+  </si>
+  <si>
+    <t>BENNE 3 POINTS GALVA 1,60 SALON + REHAUSSES</t>
+  </si>
+  <si>
+    <t>GODET HYDRAULIQUE 2,5M SALON 5 MM</t>
+  </si>
+  <si>
+    <t>BENNE A GRAPPIN TL 2,45 M SALON DOIGTS RONDS + JOUE ATT BOB CAT</t>
+  </si>
+  <si>
+    <t>BM1287206</t>
+  </si>
+  <si>
+    <t>JOUES POUR BDR TL/TRFP</t>
+  </si>
+  <si>
+    <t>JOUES POUR BAG TL/TRFP</t>
+  </si>
+  <si>
+    <t>BM1287200</t>
+  </si>
+  <si>
+    <t>BM1287624</t>
+  </si>
+  <si>
+    <t>CASQUETTE POUR BAG TL/TRFP</t>
+  </si>
+  <si>
+    <t>BM1287207</t>
+  </si>
+  <si>
+    <t>DOIGTS LATERAUX POUR GRAPPIN TL/TRFP</t>
+  </si>
+  <si>
+    <t>DOIGTS LATERAUX POUR GRAPPIN TRMP</t>
+  </si>
+  <si>
+    <t>BM1287214</t>
+  </si>
+  <si>
+    <t>BM1287215</t>
+  </si>
+  <si>
+    <t>JOUES POUR BAG TRMP</t>
+  </si>
+  <si>
+    <t>BM1287216</t>
+  </si>
+  <si>
+    <t>JOUES POUR BAG MC</t>
+  </si>
+  <si>
+    <t>BM1287217</t>
+  </si>
+  <si>
+    <t>DOIGTS LATERAUX POUR GRAPPIN MC</t>
+  </si>
+  <si>
+    <t>BM1287622</t>
+  </si>
+  <si>
+    <t>DOSSERET SOUDE POUR TABLIER</t>
+  </si>
+  <si>
+    <t>BENNE A GRAPPIN MC 0,8M SALON DOIGTS ROND + JOUES ATT EURO</t>
+  </si>
+  <si>
+    <t>BENNE A GRAPPIN TRMP 2,10M SALON DOIGTS ROND + JOUES ATT EURO</t>
+  </si>
+  <si>
+    <t>FOURCHE A GRAPPIN  TL 2,30 M SALON DOIGTS RONDS + DENTS LATERALES ATT MANITOU</t>
+  </si>
+  <si>
+    <t>BENNE A TERRE TL 2,3M SALON ATT MANITOU</t>
+  </si>
+  <si>
+    <t>BENNE GRAND VOLUME TL 2,45M/3000L SALON ATT MANITOU</t>
+  </si>
+  <si>
+    <t>PINCE ENRUBANNAGE TRMP SALON ATT EURO</t>
+  </si>
+  <si>
+    <t>PINCE MODULAIRE TRMP SALON 2X4/MAINS/PIC ATT EURO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRUNEAU </t>
+  </si>
+  <si>
+    <t>BRR</t>
+  </si>
+  <si>
+    <t>BENNE</t>
+  </si>
+  <si>
+    <t>GODET</t>
+  </si>
+  <si>
+    <t>FOURCHE</t>
   </si>
 </sst>
 </file>
@@ -3842,7 +3956,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4109,13 +4223,36 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Monétaire" xfId="1" builtinId="4"/>
     <cellStyle name="Monétaire 4" xfId="2"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -4500,11 +4637,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I587"/>
+  <dimension ref="A1:I612"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" customWidth="1"/>
-    <col min="3" max="3" width="79.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="92" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.77734375" style="65" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.77734375" style="66" customWidth="1"/>
     <col min="6" max="6" width="15.21875" bestFit="1" customWidth="1"/>
@@ -18537,11 +18674,11 @@
         <v>1756</v>
       </c>
       <c r="E485" s="11">
-        <f t="shared" ref="E485:E543" si="137">D485*0.65*0.95</f>
+        <f t="shared" ref="E485:E544" si="137">D485*0.65*0.95</f>
         <v>1084.33</v>
       </c>
       <c r="F485" s="13">
-        <f t="shared" ref="F485:F543" si="138">ROUNDUP((E485*1.25),-1)</f>
+        <f t="shared" ref="F485:F544" si="138">ROUNDUP((E485*1.25),-1)</f>
         <v>1360</v>
       </c>
       <c r="G485" s="13">
@@ -20011,55 +20148,53 @@
     </row>
     <row r="533" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A533" s="76" t="s">
-        <v>1021</v>
+        <v>1158</v>
       </c>
       <c r="B533" s="83" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="C533" s="28" t="s">
-        <v>1022</v>
+        <v>1159</v>
       </c>
       <c r="D533" s="69">
-        <v>1589</v>
+        <v>304</v>
       </c>
       <c r="E533" s="11">
         <f t="shared" si="137"/>
-        <v>981.2075000000001</v>
+        <v>187.72</v>
       </c>
       <c r="F533" s="13">
         <f t="shared" si="138"/>
-        <v>1230</v>
-      </c>
-      <c r="G533" s="13">
-        <v>90</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="G533" s="13"/>
       <c r="H533" s="21" t="s">
         <v>790</v>
       </c>
-      <c r="I533" s="21" t="s">
-        <v>1117</v>
+      <c r="I533" s="92" t="s">
+        <v>1130</v>
       </c>
     </row>
     <row r="534" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A534" s="73" t="s">
-        <v>1023</v>
+      <c r="A534" s="76" t="s">
+        <v>1021</v>
       </c>
       <c r="B534" s="83" t="s">
         <v>1124</v>
       </c>
       <c r="C534" s="28" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="D534" s="69">
-        <v>2049</v>
+        <v>1589</v>
       </c>
       <c r="E534" s="11">
         <f t="shared" si="137"/>
-        <v>1265.2575000000002</v>
+        <v>981.2075000000001</v>
       </c>
       <c r="F534" s="13">
         <f t="shared" si="138"/>
-        <v>1590</v>
+        <v>1230</v>
       </c>
       <c r="G534" s="13">
         <v>90</v>
@@ -20073,24 +20208,24 @@
     </row>
     <row r="535" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A535" s="73" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B535" s="83" t="s">
         <v>1124</v>
       </c>
       <c r="C535" s="28" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="D535" s="69">
-        <v>2467</v>
+        <v>2049</v>
       </c>
       <c r="E535" s="11">
         <f t="shared" si="137"/>
-        <v>1523.3724999999999</v>
+        <v>1265.2575000000002</v>
       </c>
       <c r="F535" s="13">
         <f t="shared" si="138"/>
-        <v>1910</v>
+        <v>1590</v>
       </c>
       <c r="G535" s="13">
         <v>90</v>
@@ -20103,25 +20238,25 @@
       </c>
     </row>
     <row r="536" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A536" s="79" t="s">
-        <v>1029</v>
+      <c r="A536" s="73" t="s">
+        <v>1025</v>
       </c>
       <c r="B536" s="83" t="s">
         <v>1124</v>
       </c>
       <c r="C536" s="28" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="D536" s="69">
-        <v>2613</v>
+        <v>2467</v>
       </c>
       <c r="E536" s="11">
         <f t="shared" si="137"/>
-        <v>1613.5274999999999</v>
+        <v>1523.3724999999999</v>
       </c>
       <c r="F536" s="13">
         <f t="shared" si="138"/>
-        <v>2020</v>
+        <v>1910</v>
       </c>
       <c r="G536" s="13">
         <v>90</v>
@@ -20129,33 +20264,33 @@
       <c r="H536" s="21" t="s">
         <v>790</v>
       </c>
-      <c r="I536" s="93" t="s">
-        <v>1116</v>
+      <c r="I536" s="21" t="s">
+        <v>1117</v>
       </c>
     </row>
     <row r="537" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A537" s="76" t="s">
-        <v>1033</v>
+      <c r="A537" s="79" t="s">
+        <v>1029</v>
       </c>
       <c r="B537" s="83" t="s">
         <v>1124</v>
       </c>
       <c r="C537" s="28" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="D537" s="69">
-        <v>2174</v>
+        <v>2613</v>
       </c>
       <c r="E537" s="11">
         <f t="shared" si="137"/>
-        <v>1342.4450000000002</v>
+        <v>1613.5274999999999</v>
       </c>
       <c r="F537" s="13">
         <f t="shared" si="138"/>
-        <v>1680</v>
+        <v>2020</v>
       </c>
       <c r="G537" s="13">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="H537" s="21" t="s">
         <v>790</v>
@@ -20165,56 +20300,56 @@
       </c>
     </row>
     <row r="538" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A538" s="73" t="s">
-        <v>1044</v>
+      <c r="A538" s="76" t="s">
+        <v>1033</v>
       </c>
       <c r="B538" s="83" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="C538" s="28" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
       <c r="D538" s="69">
-        <v>510</v>
+        <v>2174</v>
       </c>
       <c r="E538" s="11">
         <f t="shared" si="137"/>
-        <v>314.92500000000001</v>
+        <v>1342.4450000000002</v>
       </c>
       <c r="F538" s="13">
         <f t="shared" si="138"/>
-        <v>400</v>
+        <v>1680</v>
       </c>
       <c r="G538" s="13">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="H538" s="21" t="s">
         <v>790</v>
       </c>
-      <c r="I538" s="83" t="s">
-        <v>1117</v>
+      <c r="I538" s="93" t="s">
+        <v>1116</v>
       </c>
     </row>
     <row r="539" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A539" s="73" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B539" s="83" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
       <c r="C539" s="28" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D539" s="69">
-        <v>533</v>
+        <v>510</v>
       </c>
       <c r="E539" s="11">
         <f t="shared" si="137"/>
-        <v>329.1275</v>
+        <v>314.92500000000001</v>
       </c>
       <c r="F539" s="13">
         <f t="shared" si="138"/>
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="G539" s="13">
         <v>55</v>
@@ -20227,28 +20362,28 @@
       </c>
     </row>
     <row r="540" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A540" s="76" t="s">
-        <v>1048</v>
+      <c r="A540" s="73" t="s">
+        <v>1046</v>
       </c>
       <c r="B540" s="83" t="s">
         <v>1131</v>
       </c>
       <c r="C540" s="28" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="D540" s="69">
-        <v>1484</v>
+        <v>533</v>
       </c>
       <c r="E540" s="11">
         <f t="shared" si="137"/>
-        <v>916.37</v>
+        <v>329.1275</v>
       </c>
       <c r="F540" s="13">
         <f t="shared" si="138"/>
-        <v>1150</v>
+        <v>420</v>
       </c>
       <c r="G540" s="13">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="H540" s="21" t="s">
         <v>790</v>
@@ -20258,25 +20393,25 @@
       </c>
     </row>
     <row r="541" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A541" s="73" t="s">
-        <v>1050</v>
+      <c r="A541" s="76" t="s">
+        <v>1048</v>
       </c>
       <c r="B541" s="83" t="s">
         <v>1131</v>
       </c>
       <c r="C541" s="28" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="D541" s="69">
-        <v>1787</v>
+        <v>1484</v>
       </c>
       <c r="E541" s="11">
         <f t="shared" si="137"/>
-        <v>1103.4724999999999</v>
+        <v>916.37</v>
       </c>
       <c r="F541" s="13">
         <f t="shared" si="138"/>
-        <v>1380</v>
+        <v>1150</v>
       </c>
       <c r="G541" s="13">
         <v>90</v>
@@ -20290,24 +20425,24 @@
     </row>
     <row r="542" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A542" s="73" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="B542" s="83" t="s">
         <v>1131</v>
       </c>
       <c r="C542" s="28" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D542" s="69">
-        <v>1934</v>
+        <v>1787</v>
       </c>
       <c r="E542" s="11">
         <f t="shared" si="137"/>
-        <v>1194.2450000000001</v>
+        <v>1103.4724999999999</v>
       </c>
       <c r="F542" s="13">
         <f t="shared" si="138"/>
-        <v>1500</v>
+        <v>1380</v>
       </c>
       <c r="G542" s="13">
         <v>90</v>
@@ -20321,26 +20456,28 @@
     </row>
     <row r="543" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A543" s="73" t="s">
-        <v>1027</v>
+        <v>1052</v>
       </c>
       <c r="B543" s="83" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C543" s="28" t="s">
-        <v>1028</v>
+        <v>1053</v>
       </c>
       <c r="D543" s="69">
-        <v>345</v>
+        <v>1934</v>
       </c>
       <c r="E543" s="11">
         <f t="shared" si="137"/>
-        <v>213.03749999999999</v>
+        <v>1194.2450000000001</v>
       </c>
       <c r="F543" s="13">
         <f t="shared" si="138"/>
-        <v>270</v>
-      </c>
-      <c r="G543" s="13"/>
+        <v>1500</v>
+      </c>
+      <c r="G543" s="13">
+        <v>90</v>
+      </c>
       <c r="H543" s="21" t="s">
         <v>790</v>
       </c>
@@ -20349,116 +20486,116 @@
       </c>
     </row>
     <row r="544" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A544" s="79" t="s">
-        <v>1054</v>
+      <c r="A544" s="73" t="s">
+        <v>1027</v>
       </c>
       <c r="B544" s="83" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C544" s="28" t="s">
-        <v>1055</v>
+        <v>1028</v>
       </c>
       <c r="D544" s="69">
-        <v>2122</v>
+        <v>345</v>
       </c>
       <c r="E544" s="11">
-        <f t="shared" ref="E544:E587" si="139">D544*0.65*0.95</f>
-        <v>1310.3349999999998</v>
+        <f t="shared" si="137"/>
+        <v>213.03749999999999</v>
       </c>
       <c r="F544" s="13">
-        <f t="shared" ref="F544:F587" si="140">ROUNDUP((E544*1.25),-1)</f>
-        <v>1640</v>
-      </c>
-      <c r="G544" s="13">
-        <v>90</v>
-      </c>
+        <f t="shared" si="138"/>
+        <v>270</v>
+      </c>
+      <c r="G544" s="13"/>
       <c r="H544" s="21" t="s">
         <v>790</v>
       </c>
-      <c r="I544" s="93" t="s">
-        <v>1116</v>
+      <c r="I544" s="83" t="s">
+        <v>1117</v>
       </c>
     </row>
     <row r="545" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A545" s="76" t="s">
-        <v>1056</v>
+      <c r="A545" s="79" t="s">
+        <v>1054</v>
       </c>
       <c r="B545" s="83" t="s">
         <v>1131</v>
       </c>
       <c r="C545" s="28" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D545" s="69">
+        <v>2122</v>
+      </c>
+      <c r="E545" s="11">
+        <f t="shared" ref="E545:E596" si="139">D545*0.65*0.95</f>
+        <v>1310.3349999999998</v>
+      </c>
+      <c r="F545" s="13">
+        <f t="shared" ref="F545:F596" si="140">ROUNDUP((E545*1.25),-1)</f>
+        <v>1640</v>
+      </c>
+      <c r="G545" s="13">
+        <v>90</v>
+      </c>
+      <c r="H545" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="I545" s="93" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="546" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="A546" s="76" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B546" s="83" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C546" s="28" t="s">
         <v>1057</v>
       </c>
-      <c r="D545" s="69">
+      <c r="D546" s="69">
         <v>2007</v>
       </c>
-      <c r="E545" s="11">
+      <c r="E546" s="11">
         <f t="shared" si="139"/>
         <v>1239.3225</v>
       </c>
-      <c r="F545" s="13">
+      <c r="F546" s="13">
         <f t="shared" si="140"/>
         <v>1550</v>
       </c>
-      <c r="G545" s="13">
+      <c r="G546" s="13">
         <v>160</v>
       </c>
-      <c r="H545" s="21" t="s">
+      <c r="H546" s="21" t="s">
         <v>790</v>
       </c>
-      <c r="I545" s="93" t="s">
+      <c r="I546" s="93" t="s">
         <v>1116</v>
       </c>
     </row>
-    <row r="546" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A546" s="73" t="s">
+    <row r="547" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="A547" s="73" t="s">
         <v>1035</v>
       </c>
-      <c r="B546" s="83" t="s">
+      <c r="B547" s="83" t="s">
         <v>1132</v>
       </c>
-      <c r="C546" s="28" t="s">
+      <c r="C547" s="28" t="s">
         <v>1036</v>
       </c>
-      <c r="D546" s="69">
+      <c r="D547" s="69">
         <v>795</v>
       </c>
-      <c r="E546" s="11">
+      <c r="E547" s="11">
         <f t="shared" si="139"/>
         <v>490.91249999999997</v>
       </c>
-      <c r="F546" s="13">
+      <c r="F547" s="13">
         <f t="shared" si="140"/>
         <v>620</v>
-      </c>
-      <c r="G546" s="13"/>
-      <c r="H546" s="21" t="s">
-        <v>790</v>
-      </c>
-      <c r="I546" s="93" t="s">
-        <v>1116</v>
-      </c>
-    </row>
-    <row r="547" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A547" s="73" t="s">
-        <v>1037</v>
-      </c>
-      <c r="B547" s="83" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C547" s="28" t="s">
-        <v>1038</v>
-      </c>
-      <c r="D547" s="69">
-        <v>920</v>
-      </c>
-      <c r="E547" s="11">
-        <f t="shared" si="139"/>
-        <v>568.1</v>
-      </c>
-      <c r="F547" s="13">
-        <f t="shared" si="140"/>
-        <v>720</v>
       </c>
       <c r="G547" s="13"/>
       <c r="H547" s="21" t="s">
@@ -20470,24 +20607,24 @@
     </row>
     <row r="548" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A548" s="73" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="B548" s="83" t="s">
         <v>1132</v>
       </c>
       <c r="C548" s="28" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="D548" s="69">
-        <v>1056</v>
+        <v>920</v>
       </c>
       <c r="E548" s="11">
         <f t="shared" si="139"/>
-        <v>652.07999999999993</v>
+        <v>568.1</v>
       </c>
       <c r="F548" s="13">
         <f t="shared" si="140"/>
-        <v>820</v>
+        <v>720</v>
       </c>
       <c r="G548" s="13"/>
       <c r="H548" s="21" t="s">
@@ -20499,24 +20636,24 @@
     </row>
     <row r="549" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A549" s="73" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B549" s="83" t="s">
         <v>1132</v>
       </c>
       <c r="C549" s="28" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="D549" s="69">
-        <v>1040</v>
+        <v>1056</v>
       </c>
       <c r="E549" s="11">
         <f t="shared" si="139"/>
-        <v>642.19999999999993</v>
+        <v>652.07999999999993</v>
       </c>
       <c r="F549" s="13">
         <f t="shared" si="140"/>
-        <v>810</v>
+        <v>820</v>
       </c>
       <c r="G549" s="13"/>
       <c r="H549" s="21" t="s">
@@ -20527,25 +20664,25 @@
       </c>
     </row>
     <row r="550" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A550" s="75" t="s">
-        <v>1043</v>
+      <c r="A550" s="73" t="s">
+        <v>1041</v>
       </c>
       <c r="B550" s="83" t="s">
         <v>1132</v>
       </c>
       <c r="C550" s="28" t="s">
-        <v>1058</v>
+        <v>1042</v>
       </c>
       <c r="D550" s="69">
-        <v>680</v>
+        <v>1040</v>
       </c>
       <c r="E550" s="11">
         <f t="shared" si="139"/>
-        <v>419.9</v>
+        <v>642.19999999999993</v>
       </c>
       <c r="F550" s="13">
         <f t="shared" si="140"/>
-        <v>530</v>
+        <v>810</v>
       </c>
       <c r="G550" s="13"/>
       <c r="H550" s="21" t="s">
@@ -20556,50 +20693,52 @@
       </c>
     </row>
     <row r="551" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A551" s="80" t="s">
-        <v>810</v>
-      </c>
-      <c r="B551" s="83"/>
-      <c r="C551" s="71" t="s">
-        <v>811</v>
+      <c r="A551" s="75" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B551" s="83" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C551" s="28" t="s">
+        <v>1058</v>
       </c>
       <c r="D551" s="69">
-        <v>40</v>
+        <v>680</v>
       </c>
       <c r="E551" s="11">
         <f t="shared" si="139"/>
-        <v>24.7</v>
+        <v>419.9</v>
       </c>
       <c r="F551" s="13">
         <f t="shared" si="140"/>
-        <v>40</v>
+        <v>530</v>
       </c>
       <c r="G551" s="13"/>
       <c r="H551" s="21" t="s">
         <v>790</v>
       </c>
-      <c r="I551" s="83" t="s">
-        <v>1115</v>
+      <c r="I551" s="93" t="s">
+        <v>1116</v>
       </c>
     </row>
     <row r="552" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A552" s="72" t="s">
-        <v>801</v>
+      <c r="A552" s="80" t="s">
+        <v>810</v>
       </c>
       <c r="B552" s="83"/>
       <c r="C552" s="71" t="s">
-        <v>1059</v>
+        <v>811</v>
       </c>
       <c r="D552" s="69">
-        <v>314</v>
+        <v>40</v>
       </c>
       <c r="E552" s="11">
         <f t="shared" si="139"/>
-        <v>193.89499999999998</v>
+        <v>24.7</v>
       </c>
       <c r="F552" s="13">
         <f t="shared" si="140"/>
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="G552" s="13"/>
       <c r="H552" s="21" t="s">
@@ -20611,22 +20750,22 @@
     </row>
     <row r="553" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A553" s="72" t="s">
-        <v>974</v>
+        <v>801</v>
       </c>
       <c r="B553" s="83"/>
       <c r="C553" s="71" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="D553" s="69">
-        <v>136</v>
+        <v>314</v>
       </c>
       <c r="E553" s="11">
         <f t="shared" si="139"/>
-        <v>83.98</v>
+        <v>193.89499999999998</v>
       </c>
       <c r="F553" s="13">
         <f t="shared" si="140"/>
-        <v>110</v>
+        <v>250</v>
       </c>
       <c r="G553" s="13"/>
       <c r="H553" s="21" t="s">
@@ -20638,22 +20777,22 @@
     </row>
     <row r="554" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A554" s="72" t="s">
-        <v>1061</v>
+        <v>974</v>
       </c>
       <c r="B554" s="83"/>
       <c r="C554" s="71" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="D554" s="69">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="E554" s="11">
         <f t="shared" si="139"/>
-        <v>36.432499999999997</v>
+        <v>83.98</v>
       </c>
       <c r="F554" s="13">
         <f t="shared" si="140"/>
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="G554" s="13"/>
       <c r="H554" s="21" t="s">
@@ -20665,22 +20804,22 @@
     </row>
     <row r="555" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A555" s="72" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="B555" s="83"/>
       <c r="C555" s="71" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="D555" s="69">
-        <v>122</v>
+        <v>59</v>
       </c>
       <c r="E555" s="11">
         <f t="shared" si="139"/>
-        <v>75.334999999999994</v>
+        <v>36.432499999999997</v>
       </c>
       <c r="F555" s="13">
         <f t="shared" si="140"/>
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G555" s="13"/>
       <c r="H555" s="21" t="s">
@@ -20692,22 +20831,22 @@
     </row>
     <row r="556" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A556" s="72" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="B556" s="83"/>
       <c r="C556" s="71" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="D556" s="69">
-        <v>34</v>
+        <v>122</v>
       </c>
       <c r="E556" s="11">
         <f t="shared" si="139"/>
-        <v>20.995000000000001</v>
+        <v>75.334999999999994</v>
       </c>
       <c r="F556" s="13">
         <f t="shared" si="140"/>
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="G556" s="13"/>
       <c r="H556" s="21" t="s">
@@ -20719,18 +20858,18 @@
     </row>
     <row r="557" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A557" s="72" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B557" s="83"/>
       <c r="C557" s="71" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D557" s="69">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E557" s="11">
         <f t="shared" si="139"/>
-        <v>19.142500000000002</v>
+        <v>20.995000000000001</v>
       </c>
       <c r="F557" s="13">
         <f t="shared" si="140"/>
@@ -20746,22 +20885,22 @@
     </row>
     <row r="558" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A558" s="72" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="B558" s="83"/>
       <c r="C558" s="71" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="D558" s="69">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="E558" s="11">
         <f t="shared" si="139"/>
-        <v>41.99</v>
+        <v>19.142500000000002</v>
       </c>
       <c r="F558" s="13">
         <f t="shared" si="140"/>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G558" s="13"/>
       <c r="H558" s="21" t="s">
@@ -20773,22 +20912,22 @@
     </row>
     <row r="559" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A559" s="72" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B559" s="83"/>
       <c r="C559" s="71" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D559" s="69">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="E559" s="11">
         <f t="shared" si="139"/>
-        <v>56.81</v>
+        <v>41.99</v>
       </c>
       <c r="F559" s="13">
         <f t="shared" si="140"/>
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G559" s="13"/>
       <c r="H559" s="21" t="s">
@@ -20799,23 +20938,23 @@
       </c>
     </row>
     <row r="560" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A560" s="73" t="s">
-        <v>1073</v>
+      <c r="A560" s="72" t="s">
+        <v>1071</v>
       </c>
       <c r="B560" s="83"/>
       <c r="C560" s="71" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="D560" s="69">
-        <v>335</v>
+        <v>92</v>
       </c>
       <c r="E560" s="11">
         <f t="shared" si="139"/>
-        <v>206.86249999999998</v>
+        <v>56.81</v>
       </c>
       <c r="F560" s="13">
         <f t="shared" si="140"/>
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="G560" s="13"/>
       <c r="H560" s="21" t="s">
@@ -20827,22 +20966,22 @@
     </row>
     <row r="561" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A561" s="73" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="B561" s="83"/>
       <c r="C561" s="71" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="D561" s="69">
-        <v>203</v>
+        <v>335</v>
       </c>
       <c r="E561" s="11">
         <f t="shared" si="139"/>
-        <v>125.35250000000001</v>
+        <v>206.86249999999998</v>
       </c>
       <c r="F561" s="13">
         <f t="shared" si="140"/>
-        <v>160</v>
+        <v>260</v>
       </c>
       <c r="G561" s="13"/>
       <c r="H561" s="21" t="s">
@@ -20854,22 +20993,22 @@
     </row>
     <row r="562" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A562" s="73" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B562" s="83"/>
       <c r="C562" s="71" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="D562" s="69">
-        <v>320</v>
+        <v>203</v>
       </c>
       <c r="E562" s="11">
         <f t="shared" si="139"/>
-        <v>197.6</v>
+        <v>125.35250000000001</v>
       </c>
       <c r="F562" s="13">
         <f t="shared" si="140"/>
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="G562" s="13"/>
       <c r="H562" s="21" t="s">
@@ -20881,22 +21020,22 @@
     </row>
     <row r="563" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A563" s="73" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="B563" s="83"/>
       <c r="C563" s="71" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D563" s="69">
-        <v>15</v>
+        <v>320</v>
       </c>
       <c r="E563" s="11">
         <f t="shared" si="139"/>
-        <v>9.2624999999999993</v>
+        <v>197.6</v>
       </c>
       <c r="F563" s="13">
         <f t="shared" si="140"/>
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="G563" s="13"/>
       <c r="H563" s="21" t="s">
@@ -20907,23 +21046,23 @@
       </c>
     </row>
     <row r="564" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A564" s="72" t="s">
-        <v>1081</v>
+      <c r="A564" s="73" t="s">
+        <v>1079</v>
       </c>
       <c r="B564" s="83"/>
       <c r="C564" s="71" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="D564" s="69">
-        <v>526</v>
+        <v>15</v>
       </c>
       <c r="E564" s="11">
         <f t="shared" si="139"/>
-        <v>324.80500000000001</v>
+        <v>9.2624999999999993</v>
       </c>
       <c r="F564" s="13">
         <f t="shared" si="140"/>
-        <v>410</v>
+        <v>20</v>
       </c>
       <c r="G564" s="13"/>
       <c r="H564" s="21" t="s">
@@ -20934,23 +21073,23 @@
       </c>
     </row>
     <row r="565" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A565" s="73" t="s">
-        <v>1083</v>
+      <c r="A565" s="72" t="s">
+        <v>1081</v>
       </c>
       <c r="B565" s="83"/>
       <c r="C565" s="71" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="D565" s="69">
-        <v>864</v>
+        <v>526</v>
       </c>
       <c r="E565" s="11">
         <f t="shared" si="139"/>
-        <v>533.52</v>
+        <v>324.80500000000001</v>
       </c>
       <c r="F565" s="13">
         <f t="shared" si="140"/>
-        <v>670</v>
+        <v>410</v>
       </c>
       <c r="G565" s="13"/>
       <c r="H565" s="21" t="s">
@@ -20962,22 +21101,22 @@
     </row>
     <row r="566" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A566" s="73" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="B566" s="83"/>
       <c r="C566" s="71" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="D566" s="69">
-        <v>420</v>
+        <v>864</v>
       </c>
       <c r="E566" s="11">
         <f t="shared" si="139"/>
-        <v>259.34999999999997</v>
+        <v>533.52</v>
       </c>
       <c r="F566" s="13">
         <f t="shared" si="140"/>
-        <v>330</v>
+        <v>670</v>
       </c>
       <c r="G566" s="13"/>
       <c r="H566" s="21" t="s">
@@ -20988,23 +21127,23 @@
       </c>
     </row>
     <row r="567" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A567" s="81" t="s">
-        <v>1087</v>
+      <c r="A567" s="73" t="s">
+        <v>1085</v>
       </c>
       <c r="B567" s="83"/>
       <c r="C567" s="71" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="D567" s="69">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="E567" s="11">
         <f t="shared" si="139"/>
-        <v>185.25</v>
+        <v>259.34999999999997</v>
       </c>
       <c r="F567" s="13">
         <f t="shared" si="140"/>
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="G567" s="13"/>
       <c r="H567" s="21" t="s">
@@ -21016,22 +21155,22 @@
     </row>
     <row r="568" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A568" s="81" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="B568" s="83"/>
       <c r="C568" s="71" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="D568" s="69">
-        <v>327</v>
+        <v>300</v>
       </c>
       <c r="E568" s="11">
         <f t="shared" si="139"/>
-        <v>201.92250000000001</v>
+        <v>185.25</v>
       </c>
       <c r="F568" s="13">
         <f t="shared" si="140"/>
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="G568" s="13"/>
       <c r="H568" s="21" t="s">
@@ -21043,22 +21182,22 @@
     </row>
     <row r="569" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A569" s="81" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B569" s="83"/>
       <c r="C569" s="71" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="D569" s="69">
-        <v>392</v>
+        <v>327</v>
       </c>
       <c r="E569" s="11">
         <f t="shared" si="139"/>
-        <v>242.06</v>
+        <v>201.92250000000001</v>
       </c>
       <c r="F569" s="13">
         <f t="shared" si="140"/>
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="G569" s="13"/>
       <c r="H569" s="21" t="s">
@@ -21070,22 +21209,22 @@
     </row>
     <row r="570" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A570" s="81" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="B570" s="83"/>
       <c r="C570" s="71" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="D570" s="69">
-        <v>505</v>
+        <v>392</v>
       </c>
       <c r="E570" s="11">
         <f t="shared" si="139"/>
-        <v>311.83749999999998</v>
+        <v>242.06</v>
       </c>
       <c r="F570" s="13">
         <f t="shared" si="140"/>
-        <v>390</v>
+        <v>310</v>
       </c>
       <c r="G570" s="13"/>
       <c r="H570" s="21" t="s">
@@ -21096,23 +21235,23 @@
       </c>
     </row>
     <row r="571" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A571" s="73" t="s">
-        <v>1095</v>
+      <c r="A571" s="81" t="s">
+        <v>1093</v>
       </c>
       <c r="B571" s="83"/>
       <c r="C571" s="71" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="D571" s="69">
-        <v>33</v>
+        <v>505</v>
       </c>
       <c r="E571" s="11">
         <f t="shared" si="139"/>
-        <v>20.377499999999998</v>
+        <v>311.83749999999998</v>
       </c>
       <c r="F571" s="13">
         <f t="shared" si="140"/>
-        <v>30</v>
+        <v>390</v>
       </c>
       <c r="G571" s="13"/>
       <c r="H571" s="21" t="s">
@@ -21123,23 +21262,23 @@
       </c>
     </row>
     <row r="572" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A572" s="74" t="s">
-        <v>832</v>
+      <c r="A572" s="73" t="s">
+        <v>1095</v>
       </c>
       <c r="B572" s="83"/>
-      <c r="C572" s="32" t="s">
-        <v>833</v>
+      <c r="C572" s="71" t="s">
+        <v>1096</v>
       </c>
       <c r="D572" s="69">
-        <v>136</v>
+        <v>33</v>
       </c>
       <c r="E572" s="11">
         <f t="shared" si="139"/>
-        <v>83.98</v>
+        <v>20.377499999999998</v>
       </c>
       <c r="F572" s="13">
         <f t="shared" si="140"/>
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="G572" s="13"/>
       <c r="H572" s="21" t="s">
@@ -21150,23 +21289,23 @@
       </c>
     </row>
     <row r="573" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A573" s="74" t="s">
-        <v>1031</v>
+      <c r="A573" s="73" t="s">
+        <v>1142</v>
       </c>
       <c r="B573" s="83"/>
-      <c r="C573" s="70" t="s">
-        <v>1032</v>
+      <c r="C573" s="71" t="s">
+        <v>1144</v>
       </c>
       <c r="D573" s="69">
-        <v>136</v>
+        <v>230</v>
       </c>
       <c r="E573" s="11">
         <f t="shared" si="139"/>
-        <v>83.98</v>
+        <v>142.02500000000001</v>
       </c>
       <c r="F573" s="13">
         <f t="shared" si="140"/>
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="G573" s="13"/>
       <c r="H573" s="21" t="s">
@@ -21177,23 +21316,23 @@
       </c>
     </row>
     <row r="574" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A574" s="74" t="s">
-        <v>1097</v>
+      <c r="A574" s="73" t="s">
+        <v>1151</v>
       </c>
       <c r="B574" s="83"/>
-      <c r="C574" s="70" t="s">
-        <v>1098</v>
+      <c r="C574" s="71" t="s">
+        <v>1153</v>
       </c>
       <c r="D574" s="69">
-        <v>136</v>
+        <v>204</v>
       </c>
       <c r="E574" s="11">
         <f t="shared" si="139"/>
-        <v>83.98</v>
+        <v>125.96999999999998</v>
       </c>
       <c r="F574" s="13">
         <f t="shared" si="140"/>
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="G574" s="13"/>
       <c r="H574" s="21" t="s">
@@ -21205,22 +21344,22 @@
     </row>
     <row r="575" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A575" s="73" t="s">
-        <v>1099</v>
+        <v>1154</v>
       </c>
       <c r="B575" s="83"/>
       <c r="C575" s="71" t="s">
-        <v>1100</v>
+        <v>1155</v>
       </c>
       <c r="D575" s="69">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="E575" s="11">
         <f t="shared" si="139"/>
-        <v>96.33</v>
+        <v>116.7075</v>
       </c>
       <c r="F575" s="13">
         <f t="shared" si="140"/>
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="G575" s="13"/>
       <c r="H575" s="21" t="s">
@@ -21232,22 +21371,22 @@
     </row>
     <row r="576" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A576" s="73" t="s">
-        <v>1101</v>
+        <v>1148</v>
       </c>
       <c r="B576" s="83"/>
       <c r="C576" s="71" t="s">
-        <v>1102</v>
+        <v>1149</v>
       </c>
       <c r="D576" s="69">
-        <v>55</v>
+        <v>293</v>
       </c>
       <c r="E576" s="11">
         <f t="shared" si="139"/>
-        <v>33.962499999999999</v>
+        <v>180.92750000000001</v>
       </c>
       <c r="F576" s="13">
         <f t="shared" si="140"/>
-        <v>50</v>
+        <v>230</v>
       </c>
       <c r="G576" s="13"/>
       <c r="H576" s="21" t="s">
@@ -21258,23 +21397,23 @@
       </c>
     </row>
     <row r="577" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A577" s="76" t="s">
-        <v>1103</v>
+      <c r="A577" s="73" t="s">
+        <v>1152</v>
       </c>
       <c r="B577" s="83"/>
       <c r="C577" s="71" t="s">
-        <v>1104</v>
+        <v>1150</v>
       </c>
       <c r="D577" s="69">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="E577" s="11">
         <f t="shared" si="139"/>
-        <v>193.89499999999998</v>
+        <v>180.92750000000001</v>
       </c>
       <c r="F577" s="13">
         <f t="shared" si="140"/>
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="G577" s="13"/>
       <c r="H577" s="21" t="s">
@@ -21286,22 +21425,22 @@
     </row>
     <row r="578" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A578" s="73" t="s">
-        <v>1105</v>
+        <v>1156</v>
       </c>
       <c r="B578" s="83"/>
       <c r="C578" s="71" t="s">
-        <v>1106</v>
+        <v>1157</v>
       </c>
       <c r="D578" s="69">
-        <v>6</v>
+        <v>162</v>
       </c>
       <c r="E578" s="11">
         <f t="shared" si="139"/>
-        <v>3.7050000000000001</v>
+        <v>100.035</v>
       </c>
       <c r="F578" s="13">
         <f t="shared" si="140"/>
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="G578" s="13"/>
       <c r="H578" s="21" t="s">
@@ -21313,22 +21452,22 @@
     </row>
     <row r="579" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A579" s="73" t="s">
-        <v>1061</v>
+        <v>1146</v>
       </c>
       <c r="B579" s="83"/>
       <c r="C579" s="71" t="s">
-        <v>1107</v>
+        <v>1147</v>
       </c>
       <c r="D579" s="69">
-        <v>59</v>
+        <v>251</v>
       </c>
       <c r="E579" s="11">
         <f t="shared" si="139"/>
-        <v>36.432499999999997</v>
+        <v>154.99250000000001</v>
       </c>
       <c r="F579" s="13">
         <f t="shared" si="140"/>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="G579" s="13"/>
       <c r="H579" s="21" t="s">
@@ -21340,22 +21479,22 @@
     </row>
     <row r="580" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A580" s="73" t="s">
-        <v>1069</v>
+        <v>1145</v>
       </c>
       <c r="B580" s="83"/>
       <c r="C580" s="71" t="s">
-        <v>1070</v>
+        <v>1143</v>
       </c>
       <c r="D580" s="69">
-        <v>68</v>
+        <v>204</v>
       </c>
       <c r="E580" s="11">
         <f t="shared" si="139"/>
-        <v>41.99</v>
+        <v>125.96999999999998</v>
       </c>
       <c r="F580" s="13">
         <f t="shared" si="140"/>
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="G580" s="13"/>
       <c r="H580" s="21" t="s">
@@ -21366,23 +21505,23 @@
       </c>
     </row>
     <row r="581" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A581" s="72" t="s">
-        <v>1063</v>
+      <c r="A581" s="74" t="s">
+        <v>832</v>
       </c>
       <c r="B581" s="83"/>
-      <c r="C581" s="71" t="s">
-        <v>1108</v>
+      <c r="C581" s="32" t="s">
+        <v>833</v>
       </c>
       <c r="D581" s="69">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="E581" s="11">
         <f t="shared" si="139"/>
-        <v>75.334999999999994</v>
+        <v>83.98</v>
       </c>
       <c r="F581" s="13">
         <f t="shared" si="140"/>
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G581" s="13"/>
       <c r="H581" s="21" t="s">
@@ -21393,23 +21532,23 @@
       </c>
     </row>
     <row r="582" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A582" s="72" t="s">
-        <v>1067</v>
+      <c r="A582" s="74" t="s">
+        <v>1031</v>
       </c>
       <c r="B582" s="83"/>
-      <c r="C582" s="71" t="s">
-        <v>1068</v>
+      <c r="C582" s="70" t="s">
+        <v>1032</v>
       </c>
       <c r="D582" s="69">
-        <v>31</v>
+        <v>136</v>
       </c>
       <c r="E582" s="11">
         <f t="shared" si="139"/>
-        <v>19.142500000000002</v>
+        <v>83.98</v>
       </c>
       <c r="F582" s="13">
         <f t="shared" si="140"/>
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="G582" s="13"/>
       <c r="H582" s="21" t="s">
@@ -21420,23 +21559,23 @@
       </c>
     </row>
     <row r="583" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A583" s="73" t="s">
-        <v>1109</v>
+      <c r="A583" s="74" t="s">
+        <v>1097</v>
       </c>
       <c r="B583" s="83"/>
-      <c r="C583" s="71" t="s">
-        <v>1110</v>
+      <c r="C583" s="70" t="s">
+        <v>1098</v>
       </c>
       <c r="D583" s="69">
-        <v>335</v>
+        <v>136</v>
       </c>
       <c r="E583" s="11">
         <f t="shared" si="139"/>
-        <v>206.86249999999998</v>
+        <v>83.98</v>
       </c>
       <c r="F583" s="13">
         <f t="shared" si="140"/>
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="G583" s="13"/>
       <c r="H583" s="21" t="s">
@@ -21448,22 +21587,22 @@
     </row>
     <row r="584" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A584" s="73" t="s">
-        <v>1111</v>
+        <v>1099</v>
       </c>
       <c r="B584" s="83"/>
       <c r="C584" s="71" t="s">
-        <v>1112</v>
+        <v>1100</v>
       </c>
       <c r="D584" s="69">
-        <v>339</v>
+        <v>156</v>
       </c>
       <c r="E584" s="11">
         <f t="shared" si="139"/>
-        <v>209.33249999999998</v>
+        <v>96.33</v>
       </c>
       <c r="F584" s="13">
         <f t="shared" si="140"/>
-        <v>270</v>
+        <v>130</v>
       </c>
       <c r="G584" s="13"/>
       <c r="H584" s="21" t="s">
@@ -21475,22 +21614,22 @@
     </row>
     <row r="585" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A585" s="73" t="s">
-        <v>1079</v>
+        <v>1101</v>
       </c>
       <c r="B585" s="83"/>
       <c r="C585" s="71" t="s">
-        <v>1080</v>
+        <v>1102</v>
       </c>
       <c r="D585" s="69">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="E585" s="11">
         <f t="shared" si="139"/>
-        <v>9.2624999999999993</v>
+        <v>33.962499999999999</v>
       </c>
       <c r="F585" s="13">
         <f t="shared" si="140"/>
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G585" s="13"/>
       <c r="H585" s="21" t="s">
@@ -21501,23 +21640,23 @@
       </c>
     </row>
     <row r="586" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A586" s="73" t="s">
-        <v>1113</v>
+      <c r="A586" s="76" t="s">
+        <v>1103</v>
       </c>
       <c r="B586" s="83"/>
       <c r="C586" s="71" t="s">
-        <v>1114</v>
+        <v>1104</v>
       </c>
       <c r="D586" s="69">
-        <v>38</v>
+        <v>314</v>
       </c>
       <c r="E586" s="11">
         <f t="shared" si="139"/>
-        <v>23.465</v>
+        <v>193.89499999999998</v>
       </c>
       <c r="F586" s="13">
         <f t="shared" si="140"/>
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="G586" s="13"/>
       <c r="H586" s="21" t="s">
@@ -21529,22 +21668,22 @@
     </row>
     <row r="587" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="A587" s="73" t="s">
-        <v>1095</v>
+        <v>1105</v>
       </c>
       <c r="B587" s="83"/>
       <c r="C587" s="71" t="s">
-        <v>1096</v>
+        <v>1106</v>
       </c>
       <c r="D587" s="69">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="E587" s="11">
         <f t="shared" si="139"/>
-        <v>20.377499999999998</v>
+        <v>3.7050000000000001</v>
       </c>
       <c r="F587" s="13">
         <f t="shared" si="140"/>
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G587" s="13"/>
       <c r="H587" s="21" t="s">
@@ -21554,79 +21693,737 @@
         <v>1115</v>
       </c>
     </row>
+    <row r="588" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="A588" s="73" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B588" s="83"/>
+      <c r="C588" s="71" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D588" s="69">
+        <v>59</v>
+      </c>
+      <c r="E588" s="11">
+        <f t="shared" si="139"/>
+        <v>36.432499999999997</v>
+      </c>
+      <c r="F588" s="13">
+        <f t="shared" si="140"/>
+        <v>50</v>
+      </c>
+      <c r="G588" s="13"/>
+      <c r="H588" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="I588" s="83" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="589" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="A589" s="73" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B589" s="83"/>
+      <c r="C589" s="71" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D589" s="69">
+        <v>68</v>
+      </c>
+      <c r="E589" s="11">
+        <f t="shared" si="139"/>
+        <v>41.99</v>
+      </c>
+      <c r="F589" s="13">
+        <f t="shared" si="140"/>
+        <v>60</v>
+      </c>
+      <c r="G589" s="13"/>
+      <c r="H589" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="I589" s="83" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="590" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="A590" s="72" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B590" s="83"/>
+      <c r="C590" s="71" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D590" s="69">
+        <v>122</v>
+      </c>
+      <c r="E590" s="11">
+        <f t="shared" si="139"/>
+        <v>75.334999999999994</v>
+      </c>
+      <c r="F590" s="13">
+        <f t="shared" si="140"/>
+        <v>100</v>
+      </c>
+      <c r="G590" s="13"/>
+      <c r="H590" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="I590" s="83" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="591" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="A591" s="72" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B591" s="83"/>
+      <c r="C591" s="71" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D591" s="69">
+        <v>31</v>
+      </c>
+      <c r="E591" s="11">
+        <f t="shared" si="139"/>
+        <v>19.142500000000002</v>
+      </c>
+      <c r="F591" s="13">
+        <f t="shared" si="140"/>
+        <v>30</v>
+      </c>
+      <c r="G591" s="13"/>
+      <c r="H591" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="I591" s="83" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="592" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="A592" s="73" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B592" s="83"/>
+      <c r="C592" s="71" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D592" s="69">
+        <v>335</v>
+      </c>
+      <c r="E592" s="11">
+        <f t="shared" si="139"/>
+        <v>206.86249999999998</v>
+      </c>
+      <c r="F592" s="13">
+        <f t="shared" si="140"/>
+        <v>260</v>
+      </c>
+      <c r="G592" s="13"/>
+      <c r="H592" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="I592" s="83" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="593" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="A593" s="73" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B593" s="83"/>
+      <c r="C593" s="71" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D593" s="69">
+        <v>339</v>
+      </c>
+      <c r="E593" s="11">
+        <f t="shared" si="139"/>
+        <v>209.33249999999998</v>
+      </c>
+      <c r="F593" s="13">
+        <f t="shared" si="140"/>
+        <v>270</v>
+      </c>
+      <c r="G593" s="13"/>
+      <c r="H593" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="I593" s="83" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="594" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="A594" s="73" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B594" s="83"/>
+      <c r="C594" s="71" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D594" s="69">
+        <v>15</v>
+      </c>
+      <c r="E594" s="11">
+        <f t="shared" si="139"/>
+        <v>9.2624999999999993</v>
+      </c>
+      <c r="F594" s="13">
+        <f t="shared" si="140"/>
+        <v>20</v>
+      </c>
+      <c r="G594" s="13"/>
+      <c r="H594" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="I594" s="83" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="595" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="A595" s="73" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B595" s="83"/>
+      <c r="C595" s="71" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D595" s="69">
+        <v>38</v>
+      </c>
+      <c r="E595" s="11">
+        <f t="shared" si="139"/>
+        <v>23.465</v>
+      </c>
+      <c r="F595" s="13">
+        <f t="shared" si="140"/>
+        <v>30</v>
+      </c>
+      <c r="G595" s="13"/>
+      <c r="H595" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="I595" s="83" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="596" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="A596" s="73" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B596" s="83"/>
+      <c r="C596" s="71" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D596" s="69">
+        <v>33</v>
+      </c>
+      <c r="E596" s="11">
+        <f t="shared" si="139"/>
+        <v>20.377499999999998</v>
+      </c>
+      <c r="F596" s="13">
+        <f t="shared" si="140"/>
+        <v>30</v>
+      </c>
+      <c r="G596" s="13"/>
+      <c r="H596" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="I596" s="83" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="597" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="B597" s="94"/>
+      <c r="C597" s="95" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D597" s="69">
+        <v>37485</v>
+      </c>
+      <c r="E597" s="11">
+        <f>D597*0.73*0.95*0.97</f>
+        <v>25215.972074999998</v>
+      </c>
+      <c r="F597" s="13">
+        <f>ROUNDUP((E597*1.15),-1)</f>
+        <v>29000</v>
+      </c>
+      <c r="G597" s="13">
+        <v>470</v>
+      </c>
+      <c r="H597" s="21" t="s">
+        <v>1167</v>
+      </c>
+      <c r="I597" s="83" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="598" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="B598" s="94"/>
+      <c r="C598" s="95" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D598" s="69">
+        <v>33225</v>
+      </c>
+      <c r="E598" s="11">
+        <f>D598*0.73*0.95*0.97</f>
+        <v>22350.291374999997</v>
+      </c>
+      <c r="F598" s="13">
+        <f t="shared" ref="F598:F601" si="141">ROUNDUP((E598*1.15),-1)</f>
+        <v>25710</v>
+      </c>
+      <c r="G598" s="13">
+        <v>680</v>
+      </c>
+      <c r="H598" s="21" t="s">
+        <v>1167</v>
+      </c>
+      <c r="I598" s="83" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="599" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="B599" s="94"/>
+      <c r="C599" s="95" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D599" s="69">
+        <v>23413</v>
+      </c>
+      <c r="E599" s="11">
+        <f>D599*0.73*0.95*0.97</f>
+        <v>15749.808034999996</v>
+      </c>
+      <c r="F599" s="13">
+        <f t="shared" si="141"/>
+        <v>18120</v>
+      </c>
+      <c r="G599" s="13">
+        <v>680</v>
+      </c>
+      <c r="H599" s="21" t="s">
+        <v>1167</v>
+      </c>
+      <c r="I599" s="83" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="600" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="B600" s="94"/>
+      <c r="C600" s="95" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D600" s="69">
+        <v>17776</v>
+      </c>
+      <c r="E600" s="11">
+        <f>D600*0.73*0.95*0.97</f>
+        <v>11957.826319999998</v>
+      </c>
+      <c r="F600" s="13">
+        <f t="shared" si="141"/>
+        <v>13760</v>
+      </c>
+      <c r="G600" s="13">
+        <v>680</v>
+      </c>
+      <c r="H600" s="21" t="s">
+        <v>1167</v>
+      </c>
+      <c r="I600" s="83" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="601" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="B601" s="94"/>
+      <c r="C601" s="95" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D601" s="69">
+        <v>18043</v>
+      </c>
+      <c r="E601" s="11">
+        <f>D601*0.73*0.95*0.97</f>
+        <v>12137.435884999997</v>
+      </c>
+      <c r="F601" s="13">
+        <f t="shared" si="141"/>
+        <v>13960</v>
+      </c>
+      <c r="G601" s="13">
+        <v>470</v>
+      </c>
+      <c r="H601" s="21" t="s">
+        <v>1167</v>
+      </c>
+      <c r="I601" s="83" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="602" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="B602" s="94"/>
+      <c r="C602" s="95" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D602" s="69">
+        <v>1544</v>
+      </c>
+      <c r="E602" s="11">
+        <f>D602*0.73*0.95*0.97</f>
+        <v>1038.6410799999999</v>
+      </c>
+      <c r="F602" s="13">
+        <f t="shared" ref="F602:F609" si="142">ROUNDUP((E602*1.25),-1)</f>
+        <v>1300</v>
+      </c>
+      <c r="G602" s="13">
+        <v>315</v>
+      </c>
+      <c r="H602" s="21" t="s">
+        <v>1167</v>
+      </c>
+      <c r="I602" s="83" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="603" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="B603" s="94"/>
+      <c r="C603" s="95" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D603" s="69">
+        <v>3099</v>
+      </c>
+      <c r="E603" s="11">
+        <f>D603*0.73*0.95*0.97</f>
+        <v>2084.6818050000002</v>
+      </c>
+      <c r="F603" s="13">
+        <f t="shared" si="142"/>
+        <v>2610</v>
+      </c>
+      <c r="G603" s="13">
+        <v>315</v>
+      </c>
+      <c r="H603" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="I603" s="83" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="604" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="B604" s="94"/>
+      <c r="C604" s="95" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D604" s="69">
+        <v>6354</v>
+      </c>
+      <c r="E604" s="11">
+        <f>D604*0.65*0.95</f>
+        <v>3923.5950000000003</v>
+      </c>
+      <c r="F604" s="13">
+        <f t="shared" si="142"/>
+        <v>4910</v>
+      </c>
+      <c r="G604" s="13">
+        <v>160</v>
+      </c>
+      <c r="H604" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="I604" s="83" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="605" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="B605" s="94"/>
+      <c r="C605" s="95" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D605" s="69">
+        <v>4384</v>
+      </c>
+      <c r="E605" s="11">
+        <f>D605*0.65*0.95</f>
+        <v>2707.12</v>
+      </c>
+      <c r="F605" s="13">
+        <f t="shared" si="142"/>
+        <v>3390</v>
+      </c>
+      <c r="G605" s="13">
+        <v>160</v>
+      </c>
+      <c r="H605" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="I605" s="83" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="606" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="B606" s="94"/>
+      <c r="C606" s="95" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D606" s="69">
+        <v>2666</v>
+      </c>
+      <c r="E606" s="11">
+        <f t="shared" ref="E606:E611" si="143">D606*0.65*0.95</f>
+        <v>1646.2550000000001</v>
+      </c>
+      <c r="F606" s="13">
+        <f t="shared" ref="F606:F611" si="144">ROUNDUP((E606*1.25),-1)</f>
+        <v>2060</v>
+      </c>
+      <c r="G606" s="13">
+        <v>160</v>
+      </c>
+      <c r="H606" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="I606" s="83" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="607" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="B607" s="94"/>
+      <c r="C607" s="95" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D607" s="69">
+        <v>6556</v>
+      </c>
+      <c r="E607" s="11">
+        <f t="shared" si="143"/>
+        <v>4048.3300000000004</v>
+      </c>
+      <c r="F607" s="13">
+        <f t="shared" si="144"/>
+        <v>5070</v>
+      </c>
+      <c r="G607" s="13">
+        <v>160</v>
+      </c>
+      <c r="H607" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="I607" s="83" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="608" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="B608" s="94"/>
+      <c r="C608" s="95" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D608" s="69">
+        <v>2989</v>
+      </c>
+      <c r="E608" s="11">
+        <f t="shared" si="143"/>
+        <v>1845.7075</v>
+      </c>
+      <c r="F608" s="13">
+        <f t="shared" si="144"/>
+        <v>2310</v>
+      </c>
+      <c r="G608" s="13">
+        <v>160</v>
+      </c>
+      <c r="H608" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="I608" s="83" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="609" spans="2:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="B609" s="94"/>
+      <c r="C609" s="95" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D609" s="69">
+        <v>4619</v>
+      </c>
+      <c r="E609" s="11">
+        <f t="shared" si="143"/>
+        <v>2852.2324999999996</v>
+      </c>
+      <c r="F609" s="13">
+        <f t="shared" si="144"/>
+        <v>3570</v>
+      </c>
+      <c r="G609" s="13">
+        <v>160</v>
+      </c>
+      <c r="H609" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="I609" s="83" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="610" spans="2:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="B610" s="94"/>
+      <c r="C610" s="95" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D610" s="69">
+        <v>2122</v>
+      </c>
+      <c r="E610" s="11">
+        <f t="shared" si="143"/>
+        <v>1310.3349999999998</v>
+      </c>
+      <c r="F610" s="13">
+        <f t="shared" si="144"/>
+        <v>1640</v>
+      </c>
+      <c r="G610" s="13">
+        <v>90</v>
+      </c>
+      <c r="H610" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="I610" s="83" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="611" spans="2:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="B611" s="94"/>
+      <c r="C611" s="95" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D611" s="69">
+        <v>4783</v>
+      </c>
+      <c r="E611" s="11">
+        <f t="shared" si="143"/>
+        <v>2953.5025000000001</v>
+      </c>
+      <c r="F611" s="13">
+        <f t="shared" si="144"/>
+        <v>3700</v>
+      </c>
+      <c r="G611" s="13">
+        <v>160</v>
+      </c>
+      <c r="H611" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="I611" s="83" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="612" spans="2:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="B612" s="94"/>
+      <c r="C612" s="95"/>
+      <c r="D612" s="69"/>
+      <c r="E612" s="11"/>
+      <c r="F612" s="13"/>
+      <c r="G612" s="13"/>
+      <c r="H612" s="83"/>
+      <c r="I612" s="83"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C420:C433 A420:A489 C435:C489 A573 C573 A581:A582 C581:C582 A584:A587 C584:C587 A576:A578 C576:C578 A565:A571 A559:A563 A550:A557 D551:D587 C550:C571 C495:C545 A495:A545">
-    <cfRule type="expression" dxfId="14" priority="73">
+  <conditionalFormatting sqref="C420:C433 A420:A489 C435:C489 A582 C582 A590:A591 C590:C591 A593:A596 A585:A587 C585:C587 A566:A580 A560:A564 A551:A558 D552:D596 C495:C546 A495:A546 C551:C580 C593:C607">
+    <cfRule type="expression" dxfId="17" priority="76">
       <formula>NOT(MOD(ROW(),2))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C434">
-    <cfRule type="expression" dxfId="13" priority="74">
+    <cfRule type="expression" dxfId="16" priority="77">
       <formula>NOT(MOD(ROW(),2))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C572">
-    <cfRule type="expression" dxfId="12" priority="59">
+  <conditionalFormatting sqref="C581">
+    <cfRule type="expression" dxfId="15" priority="62">
       <formula>NOT(MOD(ROW(),2))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A490:A494">
-    <cfRule type="expression" dxfId="11" priority="40">
+    <cfRule type="expression" dxfId="14" priority="43">
       <formula>NOT(MOD(ROW(),2))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C490:C494">
-    <cfRule type="expression" dxfId="10" priority="39">
+    <cfRule type="expression" dxfId="13" priority="42">
       <formula>NOT(MOD(ROW(),2))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C546:C549">
-    <cfRule type="expression" dxfId="9" priority="24">
+  <conditionalFormatting sqref="C547:C550">
+    <cfRule type="expression" dxfId="12" priority="27">
       <formula>NOT(MOD(ROW(),2))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A546:A549">
-    <cfRule type="expression" dxfId="8" priority="23">
+  <conditionalFormatting sqref="A547:A550">
+    <cfRule type="expression" dxfId="11" priority="26">
       <formula>NOT(MOD(ROW(),2))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A575 C574 A572 A558">
-    <cfRule type="expression" dxfId="7" priority="21">
+  <conditionalFormatting sqref="A584 C583 A581 A559">
+    <cfRule type="expression" dxfId="10" priority="24">
       <formula>NOT(MOD(ROW(),2))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A564">
-    <cfRule type="expression" dxfId="6" priority="13">
+  <conditionalFormatting sqref="A565">
+    <cfRule type="expression" dxfId="9" priority="16">
       <formula>NOT(MOD(ROW(),2))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A583 A579:A580">
-    <cfRule type="expression" dxfId="5" priority="11">
+  <conditionalFormatting sqref="A592 A588:A589">
+    <cfRule type="expression" dxfId="8" priority="14">
       <formula>NOT(MOD(ROW(),2))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C583">
-    <cfRule type="expression" dxfId="4" priority="7">
+  <conditionalFormatting sqref="C592">
+    <cfRule type="expression" dxfId="7" priority="10">
       <formula>NOT(MOD(ROW(),2))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C575">
+  <conditionalFormatting sqref="C584">
+    <cfRule type="expression" dxfId="6" priority="8">
+      <formula>NOT(MOD(ROW(),2))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C588">
+    <cfRule type="expression" dxfId="5" priority="7">
+      <formula>NOT(MOD(ROW(),2))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C589">
+    <cfRule type="expression" dxfId="4" priority="6">
+      <formula>NOT(MOD(ROW(),2))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A583">
     <cfRule type="expression" dxfId="3" priority="5">
       <formula>NOT(MOD(ROW(),2))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C579">
-    <cfRule type="expression" dxfId="2" priority="4">
+  <conditionalFormatting sqref="D597:D607">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>NOT(MOD(ROW(),2))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C580">
-    <cfRule type="expression" dxfId="1" priority="3">
+  <conditionalFormatting sqref="C608:C612">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>NOT(MOD(ROW(),2))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A574">
-    <cfRule type="expression" dxfId="0" priority="2">
+  <conditionalFormatting sqref="D608:D612">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>NOT(MOD(ROW(),2))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/fixed.xlsx
+++ b/fixed.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2766" uniqueCount="1189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2769" uniqueCount="1190">
   <si>
     <t>Nouvelles Références 2025</t>
   </si>
@@ -3595,6 +3595,9 @@
   </si>
   <si>
     <t>25 DLP</t>
+  </si>
+  <si>
+    <t>BEATAILLERE XRB 8394 FP FP 40 - PONT PEINT - CLOISON PL - BARRIERES + LISSE</t>
   </si>
 </sst>
 </file>
@@ -4756,7 +4759,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I620"/>
+  <dimension ref="A1:I621"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" customWidth="1"/>
@@ -22343,11 +22346,11 @@
         <v>33225</v>
       </c>
       <c r="E606" s="11">
-        <f t="shared" ref="E606:E611" si="145">D606*0.73*0.95*0.97</f>
+        <f t="shared" ref="E606:E612" si="145">D606*0.73*0.95*0.97</f>
         <v>22350.291374999997</v>
       </c>
       <c r="F606" s="13">
-        <f t="shared" ref="F606:F609" si="146">ROUNDUP((E606*1.15),-1)</f>
+        <f t="shared" ref="F606:F610" si="146">ROUNDUP((E606*1.15),-1)</f>
         <v>25710</v>
       </c>
       <c r="G606" s="13">
@@ -22415,122 +22418,122 @@
     <row r="609" spans="2:9" ht="18" x14ac:dyDescent="0.3">
       <c r="B609" s="94"/>
       <c r="C609" s="95" t="s">
-        <v>1039</v>
+        <v>1189</v>
       </c>
       <c r="D609" s="69">
-        <v>18043</v>
+        <v>40919</v>
       </c>
       <c r="E609" s="11">
         <f t="shared" si="145"/>
-        <v>12137.435884999997</v>
+        <v>27526.006705</v>
       </c>
       <c r="F609" s="13">
         <f t="shared" si="146"/>
-        <v>13960</v>
+        <v>31660</v>
       </c>
       <c r="G609" s="13">
-        <v>470</v>
-      </c>
-      <c r="H609" s="21" t="s">
+        <v>680</v>
+      </c>
+      <c r="H609" s="97" t="s">
         <v>1068</v>
       </c>
       <c r="I609" s="83" t="s">
-        <v>1069</v>
+        <v>118</v>
       </c>
     </row>
     <row r="610" spans="2:9" ht="18" x14ac:dyDescent="0.3">
       <c r="B610" s="94"/>
       <c r="C610" s="95" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="D610" s="69">
-        <v>1544</v>
+        <v>18043</v>
       </c>
       <c r="E610" s="11">
         <f t="shared" si="145"/>
-        <v>1038.6410799999999</v>
+        <v>12137.435884999997</v>
       </c>
       <c r="F610" s="13">
-        <f t="shared" ref="F610:F613" si="147">ROUNDUP((E610*1.25),-1)</f>
-        <v>1300</v>
+        <f t="shared" si="146"/>
+        <v>13960</v>
       </c>
       <c r="G610" s="13">
-        <v>315</v>
+        <v>470</v>
       </c>
       <c r="H610" s="21" t="s">
         <v>1068</v>
       </c>
       <c r="I610" s="83" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="611" spans="2:9" ht="18" x14ac:dyDescent="0.3">
       <c r="B611" s="94"/>
       <c r="C611" s="95" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="D611" s="69">
-        <v>3099</v>
+        <v>1544</v>
       </c>
       <c r="E611" s="11">
         <f t="shared" si="145"/>
-        <v>2084.6818050000002</v>
+        <v>1038.6410799999999</v>
       </c>
       <c r="F611" s="13">
-        <f t="shared" si="147"/>
-        <v>2610</v>
+        <f t="shared" ref="F611:F614" si="147">ROUNDUP((E611*1.25),-1)</f>
+        <v>1300</v>
       </c>
       <c r="G611" s="13">
         <v>315</v>
       </c>
       <c r="H611" s="21" t="s">
-        <v>692</v>
+        <v>1068</v>
       </c>
       <c r="I611" s="83" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="612" spans="2:9" ht="18" x14ac:dyDescent="0.3">
       <c r="B612" s="94"/>
       <c r="C612" s="95" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="D612" s="69">
-        <v>6354</v>
+        <v>3099</v>
       </c>
       <c r="E612" s="11">
-        <f>D612*0.65*0.95</f>
-        <v>3923.5950000000003</v>
+        <f t="shared" si="145"/>
+        <v>2084.6818050000002</v>
       </c>
       <c r="F612" s="13">
         <f t="shared" si="147"/>
-        <v>4910</v>
+        <v>2610</v>
       </c>
       <c r="G612" s="13">
-        <v>160</v>
+        <v>315</v>
       </c>
       <c r="H612" s="21" t="s">
         <v>692</v>
       </c>
       <c r="I612" s="83" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="613" spans="2:9" ht="18" x14ac:dyDescent="0.3">
       <c r="B613" s="94"/>
       <c r="C613" s="95" t="s">
-        <v>1062</v>
+        <v>1042</v>
       </c>
       <c r="D613" s="69">
-        <v>4384</v>
+        <v>6354</v>
       </c>
       <c r="E613" s="11">
         <f>D613*0.65*0.95</f>
-        <v>2707.12</v>
+        <v>3923.5950000000003</v>
       </c>
       <c r="F613" s="13">
         <f t="shared" si="147"/>
-        <v>3390</v>
+        <v>4910</v>
       </c>
       <c r="G613" s="13">
         <v>160</v>
@@ -22545,18 +22548,18 @@
     <row r="614" spans="2:9" ht="18" x14ac:dyDescent="0.3">
       <c r="B614" s="94"/>
       <c r="C614" s="95" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="D614" s="69">
-        <v>2666</v>
+        <v>4384</v>
       </c>
       <c r="E614" s="11">
-        <f t="shared" ref="E614:E619" si="148">D614*0.65*0.95</f>
-        <v>1646.2550000000001</v>
+        <f>D614*0.65*0.95</f>
+        <v>2707.12</v>
       </c>
       <c r="F614" s="13">
-        <f t="shared" ref="F614:F619" si="149">ROUNDUP((E614*1.25),-1)</f>
-        <v>2060</v>
+        <f t="shared" si="147"/>
+        <v>3390</v>
       </c>
       <c r="G614" s="13">
         <v>160</v>
@@ -22571,18 +22574,18 @@
     <row r="615" spans="2:9" ht="18" x14ac:dyDescent="0.3">
       <c r="B615" s="94"/>
       <c r="C615" s="95" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="D615" s="69">
-        <v>6556</v>
+        <v>2666</v>
       </c>
       <c r="E615" s="11">
-        <f t="shared" si="148"/>
-        <v>4048.3300000000004</v>
+        <f t="shared" ref="E615:E620" si="148">D615*0.65*0.95</f>
+        <v>1646.2550000000001</v>
       </c>
       <c r="F615" s="13">
-        <f t="shared" si="149"/>
-        <v>5070</v>
+        <f t="shared" ref="F615:F620" si="149">ROUNDUP((E615*1.25),-1)</f>
+        <v>2060</v>
       </c>
       <c r="G615" s="13">
         <v>160</v>
@@ -22591,24 +22594,24 @@
         <v>692</v>
       </c>
       <c r="I615" s="83" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="616" spans="2:9" ht="18" x14ac:dyDescent="0.3">
       <c r="B616" s="94"/>
       <c r="C616" s="95" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="D616" s="69">
-        <v>2989</v>
+        <v>6556</v>
       </c>
       <c r="E616" s="11">
         <f t="shared" si="148"/>
-        <v>1845.7075</v>
+        <v>4048.3300000000004</v>
       </c>
       <c r="F616" s="13">
         <f t="shared" si="149"/>
-        <v>2310</v>
+        <v>5070</v>
       </c>
       <c r="G616" s="13">
         <v>160</v>
@@ -22617,24 +22620,24 @@
         <v>692</v>
       </c>
       <c r="I616" s="83" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="617" spans="2:9" ht="18" x14ac:dyDescent="0.3">
       <c r="B617" s="94"/>
       <c r="C617" s="95" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="D617" s="69">
-        <v>4619</v>
+        <v>2989</v>
       </c>
       <c r="E617" s="11">
         <f t="shared" si="148"/>
-        <v>2852.2324999999996</v>
+        <v>1845.7075</v>
       </c>
       <c r="F617" s="13">
         <f t="shared" si="149"/>
-        <v>3570</v>
+        <v>2310</v>
       </c>
       <c r="G617" s="13">
         <v>160</v>
@@ -22649,47 +22652,47 @@
     <row r="618" spans="2:9" ht="18" x14ac:dyDescent="0.3">
       <c r="B618" s="94"/>
       <c r="C618" s="95" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="D618" s="69">
-        <v>2122</v>
+        <v>4619</v>
       </c>
       <c r="E618" s="11">
         <f t="shared" si="148"/>
-        <v>1310.3349999999998</v>
+        <v>2852.2324999999996</v>
       </c>
       <c r="F618" s="13">
         <f t="shared" si="149"/>
-        <v>1640</v>
+        <v>3570</v>
       </c>
       <c r="G618" s="13">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="H618" s="21" t="s">
         <v>692</v>
       </c>
       <c r="I618" s="83" t="s">
-        <v>1018</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="619" spans="2:9" ht="18" x14ac:dyDescent="0.3">
       <c r="B619" s="94"/>
       <c r="C619" s="95" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="D619" s="69">
-        <v>4783</v>
+        <v>2122</v>
       </c>
       <c r="E619" s="11">
         <f t="shared" si="148"/>
-        <v>2953.5025000000001</v>
+        <v>1310.3349999999998</v>
       </c>
       <c r="F619" s="13">
         <f t="shared" si="149"/>
-        <v>3700</v>
+        <v>1640</v>
       </c>
       <c r="G619" s="13">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="H619" s="21" t="s">
         <v>692</v>
@@ -22700,16 +22703,42 @@
     </row>
     <row r="620" spans="2:9" ht="18" x14ac:dyDescent="0.3">
       <c r="B620" s="94"/>
-      <c r="C620" s="95"/>
-      <c r="D620" s="69"/>
-      <c r="E620" s="11"/>
-      <c r="F620" s="13"/>
-      <c r="G620" s="13"/>
-      <c r="H620" s="83"/>
-      <c r="I620" s="83"/>
+      <c r="C620" s="95" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D620" s="69">
+        <v>4783</v>
+      </c>
+      <c r="E620" s="11">
+        <f t="shared" si="148"/>
+        <v>2953.5025000000001</v>
+      </c>
+      <c r="F620" s="13">
+        <f t="shared" si="149"/>
+        <v>3700</v>
+      </c>
+      <c r="G620" s="13">
+        <v>160</v>
+      </c>
+      <c r="H620" s="21" t="s">
+        <v>692</v>
+      </c>
+      <c r="I620" s="83" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="621" spans="2:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="B621" s="94"/>
+      <c r="C621" s="95"/>
+      <c r="D621" s="69"/>
+      <c r="E621" s="11"/>
+      <c r="F621" s="13"/>
+      <c r="G621" s="13"/>
+      <c r="H621" s="83"/>
+      <c r="I621" s="83"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C429:C442 A429:A498 C444:C498 A591 C591 A599:A600 C599:C600 A602:A605 A594:A596 C594:C596 A575:A589 A569:A573 A560:A567 D561:D605 C504:C555 A504:A555 C560:C589 C602:C605 C606:D615">
+  <conditionalFormatting sqref="C429:C442 A429:A498 C444:C498 A591 C591 A599:A600 C599:C600 A602:A605 A594:A596 C594:C596 A575:A589 A569:A573 A560:A567 D561:D605 C504:C555 A504:A555 C560:C589 C602:C605 C606:D616">
     <cfRule type="expression" dxfId="16" priority="76">
       <formula>NOT(MOD(ROW(),2))</formula>
     </cfRule>
@@ -22784,12 +22813,12 @@
       <formula>NOT(MOD(ROW(),2))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C616:C620">
+  <conditionalFormatting sqref="C617:C621">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>NOT(MOD(ROW(),2))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D616:D620">
+  <conditionalFormatting sqref="D617:D621">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>NOT(MOD(ROW(),2))</formula>
     </cfRule>
